--- a/toolkit/savings-funnel-tracker.xlsx
+++ b/toolkit/savings-funnel-tracker.xlsx
@@ -557,9 +557,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-    </row>
+    <row r="4"/>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
@@ -580,7 +578,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Logged with an owner and a rough saving — no validation yet.</t>
+          <t>Captured with the function, a rough saving and an owner. Nothing checked yet.</t>
         </is>
       </c>
     </row>
@@ -592,31 +590,31 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>Business case drafted: saving, one-time cost, risk and validation plan agreed.</t>
+          <t>Technical feasibility confirmed, saving checked by finance, one-time cost estimated.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>L3 · Implemented</t>
+          <t>L3 · Approved</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Change made in production / PPAP cleared.</t>
+          <t>Business case approved by the value board; budget and people committed.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>L4 · Audited</t>
+          <t>L4 · Implemented</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Saving confirmed against the frozen baseline by finance — now it counts.</t>
+          <t>Change in production (PPAP / validation complete) and the saving checked by finance against the fixed starting cost. Only now does it count.</t>
         </is>
       </c>
     </row>
@@ -679,9 +677,8 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-    </row>
+    <row r="4"/>
+    <row r="5"/>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
@@ -780,7 +777,7 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>L3 Implemented</t>
+          <t>L3 Approved</t>
         </is>
       </c>
       <c r="D8" s="9" t="n">
@@ -1450,6 +1447,7 @@
         <v/>
       </c>
     </row>
+    <row r="55"/>
     <row r="56" ht="28" customHeight="1">
       <c r="A56" s="14" t="inlineStr">
         <is>
@@ -1457,6 +1455,7 @@
         </is>
       </c>
     </row>
+    <row r="57"/>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
@@ -1474,7 +1473,7 @@
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 C17 C18 C19 C20 C21 C22 C23 C24 C25 C26 C27 C28 C29 C30 C31 C32 C33 C34 C35 C36 C37 C38 C39 C40 C41 C42 C43 C44 C45 C46 C47 C48 C49 C50 C51 C52 C53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"L1 Idea,L2 Validated,L3 Implemented,L4 Audited"</formula1>
+      <formula1>"L1 Idea,L2 Validated,L3 Approved,L4 Implemented"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/toolkit/savings-funnel-tracker.xlsx
+++ b/toolkit/savings-funnel-tracker.xlsx
@@ -557,7 +557,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
@@ -677,8 +676,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
@@ -697,12 +694,12 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Gross saving €/yr</t>
+          <t>Gross saving £/yr</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>One-time cost €</t>
+          <t>One-time cost £</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -760,7 +757,7 @@
       <c r="H7" s="8" t="inlineStr"/>
       <c r="I7" s="8" t="inlineStr">
         <is>
-          <t>CAE sign-off pending</t>
+          <t>Saving checked by finance; awaiting board</t>
         </is>
       </c>
     </row>
@@ -1435,7 +1432,7 @@
     <row r="54">
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>Total pipeline €/yr →</t>
+          <t>Total pipeline £/yr →</t>
         </is>
       </c>
       <c r="D54" s="13">
@@ -1447,7 +1444,6 @@
         <v/>
       </c>
     </row>
-    <row r="55"/>
     <row r="56" ht="28" customHeight="1">
       <c r="A56" s="14" t="inlineStr">
         <is>
@@ -1455,7 +1451,6 @@
         </is>
       </c>
     </row>
-    <row r="57"/>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
